--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{3CFB2CE0-9FF9-4035-A407-178AEB2296F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CE8E520-ECDF-45B0-AD72-8B2A7D70A1BB}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{3CFB2CE0-9FF9-4035-A407-178AEB2296F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6654E707-F354-419E-A5EB-349376BD7850}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2197" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2197" uniqueCount="521">
   <si>
     <t>Date</t>
   </si>
@@ -1586,9 +1586,6 @@
   </si>
   <si>
     <t>Mikel Landa</t>
-  </si>
-  <si>
-    <t>Jørgen Nordhagen</t>
   </si>
 </sst>
 </file>
@@ -9491,7 +9488,7 @@
         <v>394</v>
       </c>
       <c r="J183" t="s">
-        <v>521</v>
+        <v>119</v>
       </c>
       <c r="K183" t="s">
         <v>377</v>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{3CFB2CE0-9FF9-4035-A407-178AEB2296F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6654E707-F354-419E-A5EB-349376BD7850}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="8_{3CFB2CE0-9FF9-4035-A407-178AEB2296F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B44F1836-6323-4226-BC59-295B81044315}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2197" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2221" uniqueCount="523">
   <si>
     <t>Date</t>
   </si>
@@ -1586,6 +1586,12 @@
   </si>
   <si>
     <t>Mikel Landa</t>
+  </si>
+  <si>
+    <t>Pau Martí</t>
+  </si>
+  <si>
+    <t>Grand Prix Cycliste de Montréal</t>
   </si>
 </sst>
 </file>
@@ -1984,7 +1990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M183"/>
+  <dimension ref="A1:M185"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
@@ -9498,6 +9504,88 @@
       </c>
       <c r="M183" t="s">
         <v>244</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A184" s="1">
+        <v>46278</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C184" t="s">
+        <v>407</v>
+      </c>
+      <c r="D184" t="s">
+        <v>107</v>
+      </c>
+      <c r="E184" t="s">
+        <v>103</v>
+      </c>
+      <c r="F184" t="s">
+        <v>313</v>
+      </c>
+      <c r="G184" t="s">
+        <v>27</v>
+      </c>
+      <c r="H184" t="s">
+        <v>496</v>
+      </c>
+      <c r="I184" t="s">
+        <v>307</v>
+      </c>
+      <c r="J184" t="s">
+        <v>48</v>
+      </c>
+      <c r="K184" t="s">
+        <v>297</v>
+      </c>
+      <c r="L184" t="s">
+        <v>521</v>
+      </c>
+      <c r="M184" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A185" s="1">
+        <v>46278</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C185" t="s">
+        <v>60</v>
+      </c>
+      <c r="D185" t="s">
+        <v>469</v>
+      </c>
+      <c r="E185" t="s">
+        <v>137</v>
+      </c>
+      <c r="F185" t="s">
+        <v>79</v>
+      </c>
+      <c r="G185" t="s">
+        <v>289</v>
+      </c>
+      <c r="H185" t="s">
+        <v>74</v>
+      </c>
+      <c r="I185" t="s">
+        <v>204</v>
+      </c>
+      <c r="J185" t="s">
+        <v>218</v>
+      </c>
+      <c r="K185" t="s">
+        <v>226</v>
+      </c>
+      <c r="L185" t="s">
+        <v>281</v>
+      </c>
+      <c r="M185" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -325,7 +325,7 @@
     <t>UAE Tour</t>
   </si>
   <si>
-    <t>Isaac del Toro</t>
+    <t>Isaac Del Toro</t>
   </si>
   <si>
     <t>Cees Bol</t>
@@ -1471,7 +1471,7 @@
     <t>Alessandro Borgo</t>
   </si>
   <si>
-    <t>Tim Van Dijke</t>
+    <t>Tim van Dijke</t>
   </si>
   <si>
     <t>Stefano Oldani</t>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{3CFB2CE0-9FF9-4035-A407-178AEB2296F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B44F1836-6323-4226-BC59-295B81044315}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{3CFB2CE0-9FF9-4035-A407-178AEB2296F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05E977B7-1482-4CA7-BA61-5742AC6BD601}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2221" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2233" uniqueCount="524">
   <si>
     <t>Date</t>
   </si>
@@ -1592,6 +1592,9 @@
   </si>
   <si>
     <t>Grand Prix Cycliste de Montréal</t>
+  </si>
+  <si>
+    <t>Gran Premio città di Peccioli - Coppa Sabatini</t>
   </si>
 </sst>
 </file>
@@ -1990,20 +1993,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M185"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M186"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="27" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="13" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2044,7 +2047,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46042</v>
       </c>
@@ -2085,7 +2088,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46043</v>
       </c>
@@ -2126,7 +2129,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46044</v>
       </c>
@@ -2167,7 +2170,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46045</v>
       </c>
@@ -2208,7 +2211,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46046</v>
       </c>
@@ -2249,7 +2252,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46047</v>
       </c>
@@ -2290,7 +2293,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -2331,7 +2334,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46057</v>
       </c>
@@ -2372,7 +2375,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46058</v>
       </c>
@@ -2413,7 +2416,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46059</v>
       </c>
@@ -2454,7 +2457,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46060</v>
       </c>
@@ -2495,7 +2498,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46061</v>
       </c>
@@ -2536,7 +2539,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46069</v>
       </c>
@@ -2577,7 +2580,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46070</v>
       </c>
@@ -2618,7 +2621,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46071</v>
       </c>
@@ -2659,7 +2662,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46071</v>
       </c>
@@ -2700,7 +2703,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46072</v>
       </c>
@@ -2741,7 +2744,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46072</v>
       </c>
@@ -2782,7 +2785,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46073</v>
       </c>
@@ -2823,7 +2826,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46073</v>
       </c>
@@ -2864,7 +2867,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46074</v>
       </c>
@@ -2905,7 +2908,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46074</v>
       </c>
@@ -2946,7 +2949,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46075</v>
       </c>
@@ -2987,7 +2990,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46075</v>
       </c>
@@ -3028,7 +3031,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46081</v>
       </c>
@@ -3069,7 +3072,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46081</v>
       </c>
@@ -3110,7 +3113,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46082</v>
       </c>
@@ -3151,7 +3154,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46082</v>
       </c>
@@ -3192,7 +3195,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46088</v>
       </c>
@@ -3233,7 +3236,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46089</v>
       </c>
@@ -3274,7 +3277,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>46090</v>
       </c>
@@ -3315,7 +3318,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>46091</v>
       </c>
@@ -3356,7 +3359,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>46092</v>
       </c>
@@ -3397,7 +3400,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>46092</v>
       </c>
@@ -3438,7 +3441,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>46093</v>
       </c>
@@ -3479,7 +3482,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>46093</v>
       </c>
@@ -3520,7 +3523,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>46094</v>
       </c>
@@ -3561,7 +3564,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>46094</v>
       </c>
@@ -3602,7 +3605,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>46095</v>
       </c>
@@ -3643,7 +3646,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>46095</v>
       </c>
@@ -3684,7 +3687,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>46096</v>
       </c>
@@ -3725,7 +3728,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>46096</v>
       </c>
@@ -3766,7 +3769,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>46099</v>
       </c>
@@ -3807,7 +3810,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>46099</v>
       </c>
@@ -3848,7 +3851,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>46102</v>
       </c>
@@ -3889,7 +3892,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46104</v>
       </c>
@@ -3930,7 +3933,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46105</v>
       </c>
@@ -3971,7 +3974,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>46106</v>
       </c>
@@ -4012,7 +4015,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>46106</v>
       </c>
@@ -4053,7 +4056,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>46107</v>
       </c>
@@ -4094,7 +4097,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>46108</v>
       </c>
@@ -4135,7 +4138,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>46108</v>
       </c>
@@ -4176,7 +4179,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>46109</v>
       </c>
@@ -4217,7 +4220,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>46110</v>
       </c>
@@ -4258,7 +4261,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>46110</v>
       </c>
@@ -4299,7 +4302,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>46113</v>
       </c>
@@ -4340,7 +4343,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>46116</v>
       </c>
@@ -4381,7 +4384,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>46117</v>
       </c>
@@ -4422,7 +4425,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>46118</v>
       </c>
@@ -4463,7 +4466,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>46119</v>
       </c>
@@ -4504,7 +4507,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>46120</v>
       </c>
@@ -4545,7 +4548,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>46120</v>
       </c>
@@ -4586,7 +4589,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>46121</v>
       </c>
@@ -4627,7 +4630,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>46122</v>
       </c>
@@ -4668,7 +4671,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>46123</v>
       </c>
@@ -4709,7 +4712,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>46124</v>
       </c>
@@ -4750,7 +4753,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>46127</v>
       </c>
@@ -4791,7 +4794,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>46131</v>
       </c>
@@ -4832,7 +4835,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>46132</v>
       </c>
@@ -4873,7 +4876,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>46133</v>
       </c>
@@ -4914,7 +4917,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>46134</v>
       </c>
@@ -4955,7 +4958,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>46134</v>
       </c>
@@ -4996,7 +4999,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>46135</v>
       </c>
@@ -5037,7 +5040,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>46136</v>
       </c>
@@ -5078,7 +5081,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>46138</v>
       </c>
@@ -5119,7 +5122,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>46140</v>
       </c>
@@ -5160,7 +5163,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>46141</v>
       </c>
@@ -5201,7 +5204,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>46142</v>
       </c>
@@ -5242,7 +5245,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>46143</v>
       </c>
@@ -5283,7 +5286,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>46143</v>
       </c>
@@ -5324,7 +5327,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>46144</v>
       </c>
@@ -5365,7 +5368,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>46145</v>
       </c>
@@ -5406,7 +5409,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>46150</v>
       </c>
@@ -5447,7 +5450,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>46151</v>
       </c>
@@ -5488,7 +5491,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>46152</v>
       </c>
@@ -5529,7 +5532,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>46154</v>
       </c>
@@ -5570,7 +5573,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>46155</v>
       </c>
@@ -5611,7 +5614,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>46156</v>
       </c>
@@ -5652,7 +5655,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>46157</v>
       </c>
@@ -5693,7 +5696,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>46158</v>
       </c>
@@ -5734,7 +5737,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>46159</v>
       </c>
@@ -5775,7 +5778,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>46161</v>
       </c>
@@ -5816,7 +5819,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>46162</v>
       </c>
@@ -5857,7 +5860,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>46163</v>
       </c>
@@ -5898,7 +5901,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>46164</v>
       </c>
@@ -5939,7 +5942,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>46165</v>
       </c>
@@ -5980,7 +5983,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>46166</v>
       </c>
@@ -6021,7 +6024,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>46168</v>
       </c>
@@ -6062,7 +6065,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>46169</v>
       </c>
@@ -6103,7 +6106,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>46170</v>
       </c>
@@ -6144,7 +6147,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>46171</v>
       </c>
@@ -6185,7 +6188,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>46172</v>
       </c>
@@ -6226,7 +6229,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>46173</v>
       </c>
@@ -6267,7 +6270,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>46180</v>
       </c>
@@ -6308,7 +6311,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>46180</v>
       </c>
@@ -6349,7 +6352,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>46181</v>
       </c>
@@ -6390,7 +6393,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>46183</v>
       </c>
@@ -6431,7 +6434,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>46184</v>
       </c>
@@ -6472,7 +6475,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>46185</v>
       </c>
@@ -6513,7 +6516,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>46186</v>
       </c>
@@ -6554,7 +6557,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>46187</v>
       </c>
@@ -6595,7 +6598,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>46187</v>
       </c>
@@ -6636,7 +6639,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>46190</v>
       </c>
@@ -6677,7 +6680,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>46191</v>
       </c>
@@ -6718,7 +6721,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>46192</v>
       </c>
@@ -6759,7 +6762,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>46193</v>
       </c>
@@ -6800,7 +6803,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>46194</v>
       </c>
@@ -6841,7 +6844,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>46208</v>
       </c>
@@ -6882,7 +6885,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>46209</v>
       </c>
@@ -6923,7 +6926,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>46210</v>
       </c>
@@ -6964,7 +6967,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>46211</v>
       </c>
@@ -7005,7 +7008,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>46212</v>
       </c>
@@ -7046,7 +7049,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>46213</v>
       </c>
@@ -7087,7 +7090,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>46214</v>
       </c>
@@ -7128,7 +7131,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>46215</v>
       </c>
@@ -7169,7 +7172,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>46217</v>
       </c>
@@ -7210,7 +7213,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>46218</v>
       </c>
@@ -7251,7 +7254,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>46219</v>
       </c>
@@ -7292,7 +7295,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>46220</v>
       </c>
@@ -7333,7 +7336,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>46221</v>
       </c>
@@ -7374,7 +7377,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>46222</v>
       </c>
@@ -7415,7 +7418,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>46224</v>
       </c>
@@ -7456,7 +7459,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>46225</v>
       </c>
@@ -7497,7 +7500,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>46226</v>
       </c>
@@ -7538,7 +7541,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>46227</v>
       </c>
@@ -7579,7 +7582,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>46228</v>
       </c>
@@ -7620,7 +7623,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>46229</v>
       </c>
@@ -7661,7 +7664,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>46235</v>
       </c>
@@ -7702,7 +7705,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>46237</v>
       </c>
@@ -7743,7 +7746,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>46238</v>
       </c>
@@ -7784,7 +7787,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>46239</v>
       </c>
@@ -7825,7 +7828,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>46240</v>
       </c>
@@ -7866,7 +7869,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>46241</v>
       </c>
@@ -7907,7 +7910,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>46242</v>
       </c>
@@ -7948,7 +7951,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>46243</v>
       </c>
@@ -7989,7 +7992,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>46250</v>
       </c>
@@ -8030,7 +8033,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>46253</v>
       </c>
@@ -8071,7 +8074,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>46253</v>
       </c>
@@ -8112,7 +8115,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>46254</v>
       </c>
@@ -8153,7 +8156,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>46254</v>
       </c>
@@ -8194,7 +8197,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>46255</v>
       </c>
@@ -8235,7 +8238,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>46255</v>
       </c>
@@ -8276,7 +8279,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>46256</v>
       </c>
@@ -8317,7 +8320,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>46256</v>
       </c>
@@ -8358,7 +8361,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>46256</v>
       </c>
@@ -8399,7 +8402,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>46257</v>
       </c>
@@ -8440,7 +8443,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>46257</v>
       </c>
@@ -8481,7 +8484,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>46257</v>
       </c>
@@ -8522,7 +8525,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>46259</v>
       </c>
@@ -8563,7 +8566,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>46260</v>
       </c>
@@ -8604,7 +8607,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>46261</v>
       </c>
@@ -8645,7 +8648,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>46262</v>
       </c>
@@ -8686,7 +8689,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>46263</v>
       </c>
@@ -8727,7 +8730,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>46264</v>
       </c>
@@ -8768,7 +8771,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>46264</v>
       </c>
@@ -8809,7 +8812,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>46266</v>
       </c>
@@ -8850,7 +8853,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>46267</v>
       </c>
@@ -8891,7 +8894,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>46267</v>
       </c>
@@ -8932,7 +8935,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>46268</v>
       </c>
@@ -8973,7 +8976,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>46268</v>
       </c>
@@ -9014,7 +9017,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>46269</v>
       </c>
@@ -9055,7 +9058,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>46269</v>
       </c>
@@ -9096,7 +9099,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A174" s="3">
         <v>46270</v>
       </c>
@@ -9137,7 +9140,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" s="3">
         <v>46271</v>
       </c>
@@ -9178,7 +9181,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A176" s="3">
         <v>46270</v>
       </c>
@@ -9219,7 +9222,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A177" s="3">
         <v>46271</v>
       </c>
@@ -9260,7 +9263,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A178" s="3">
         <v>46273</v>
       </c>
@@ -9301,7 +9304,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A179" s="3">
         <v>46274</v>
       </c>
@@ -9342,7 +9345,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A180" s="3">
         <v>46275</v>
       </c>
@@ -9383,7 +9386,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>46276</v>
       </c>
@@ -9424,7 +9427,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>46276</v>
       </c>
@@ -9465,7 +9468,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>46277</v>
       </c>
@@ -9506,7 +9509,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>46278</v>
       </c>
@@ -9547,7 +9550,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>46278</v>
       </c>
@@ -9586,6 +9589,47 @@
       </c>
       <c r="M185" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A186" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B186" t="s">
+        <v>523</v>
+      </c>
+      <c r="C186" t="s">
+        <v>60</v>
+      </c>
+      <c r="D186" t="s">
+        <v>317</v>
+      </c>
+      <c r="E186" t="s">
+        <v>195</v>
+      </c>
+      <c r="F186" t="s">
+        <v>188</v>
+      </c>
+      <c r="G186" t="s">
+        <v>192</v>
+      </c>
+      <c r="H186" t="s">
+        <v>193</v>
+      </c>
+      <c r="I186" t="s">
+        <v>89</v>
+      </c>
+      <c r="J186" t="s">
+        <v>499</v>
+      </c>
+      <c r="K186" t="s">
+        <v>371</v>
+      </c>
+      <c r="L186" t="s">
+        <v>391</v>
+      </c>
+      <c r="M186" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{3CFB2CE0-9FF9-4035-A407-178AEB2296F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05E977B7-1482-4CA7-BA61-5742AC6BD601}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CC810A7-098C-45FC-9C3F-E317D84C376C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2233" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2257" uniqueCount="529">
   <si>
     <t>Date</t>
   </si>
@@ -1595,6 +1595,21 @@
   </si>
   <si>
     <t>Gran Premio città di Peccioli - Coppa Sabatini</t>
+  </si>
+  <si>
+    <t>Flandrien 0.0 Classic</t>
+  </si>
+  <si>
+    <t>Henrik Pedersen</t>
+  </si>
+  <si>
+    <t>Thibaud Gruel</t>
+  </si>
+  <si>
+    <t>World Championship - Time Trial</t>
+  </si>
+  <si>
+    <t>Kasper Asgreen</t>
   </si>
 </sst>
 </file>
@@ -1993,7 +2008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M186"/>
+  <dimension ref="A1:M188"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -9630,6 +9645,88 @@
       </c>
       <c r="M186" t="s">
         <v>194</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A187" s="1">
+        <v>46284</v>
+      </c>
+      <c r="B187" t="s">
+        <v>524</v>
+      </c>
+      <c r="C187" t="s">
+        <v>60</v>
+      </c>
+      <c r="D187" t="s">
+        <v>525</v>
+      </c>
+      <c r="E187" t="s">
+        <v>17</v>
+      </c>
+      <c r="F187" t="s">
+        <v>77</v>
+      </c>
+      <c r="G187" t="s">
+        <v>477</v>
+      </c>
+      <c r="H187" t="s">
+        <v>22</v>
+      </c>
+      <c r="I187" t="s">
+        <v>526</v>
+      </c>
+      <c r="J187" t="s">
+        <v>250</v>
+      </c>
+      <c r="K187" t="s">
+        <v>174</v>
+      </c>
+      <c r="L187" t="s">
+        <v>33</v>
+      </c>
+      <c r="M187" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A188" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B188" t="s">
+        <v>527</v>
+      </c>
+      <c r="C188" t="s">
+        <v>60</v>
+      </c>
+      <c r="D188" t="s">
+        <v>74</v>
+      </c>
+      <c r="E188" t="s">
+        <v>152</v>
+      </c>
+      <c r="F188" t="s">
+        <v>137</v>
+      </c>
+      <c r="G188" t="s">
+        <v>79</v>
+      </c>
+      <c r="H188" t="s">
+        <v>153</v>
+      </c>
+      <c r="I188" t="s">
+        <v>100</v>
+      </c>
+      <c r="J188" t="s">
+        <v>155</v>
+      </c>
+      <c r="K188" t="s">
+        <v>528</v>
+      </c>
+      <c r="L188" t="s">
+        <v>111</v>
+      </c>
+      <c r="M188" t="s">
+        <v>465</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CC810A7-098C-45FC-9C3F-E317D84C376C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F46C83E-0229-425E-AA06-B15FFB41A5CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2257" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2269" uniqueCount="531">
   <si>
     <t>Date</t>
   </si>
@@ -1610,6 +1610,12 @@
   </si>
   <si>
     <t>Kasper Asgreen</t>
+  </si>
+  <si>
+    <t>Mathieu Van Der Poel</t>
+  </si>
+  <si>
+    <t>World Championships - Road Race</t>
   </si>
 </sst>
 </file>
@@ -2008,7 +2014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M188"/>
+  <dimension ref="A1:M189"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -9727,6 +9733,47 @@
       </c>
       <c r="M188" t="s">
         <v>465</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A189" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B189" t="s">
+        <v>530</v>
+      </c>
+      <c r="C189" t="s">
+        <v>60</v>
+      </c>
+      <c r="D189" t="s">
+        <v>79</v>
+      </c>
+      <c r="E189" t="s">
+        <v>439</v>
+      </c>
+      <c r="F189" t="s">
+        <v>529</v>
+      </c>
+      <c r="G189" t="s">
+        <v>289</v>
+      </c>
+      <c r="H189" t="s">
+        <v>100</v>
+      </c>
+      <c r="I189" t="s">
+        <v>255</v>
+      </c>
+      <c r="J189" t="s">
+        <v>204</v>
+      </c>
+      <c r="K189" t="s">
+        <v>180</v>
+      </c>
+      <c r="L189" t="s">
+        <v>218</v>
+      </c>
+      <c r="M189" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DPshonyak\OneDrive - BluCurrent Credit Union\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F46C83E-0229-425E-AA06-B15FFB41A5CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9B13DC4-226E-42DF-84DD-1977783972A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2269" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2305" uniqueCount="535">
   <si>
     <t>Date</t>
   </si>
@@ -1616,6 +1616,18 @@
   </si>
   <si>
     <t>World Championships - Road Race</t>
+  </si>
+  <si>
+    <t>Sparkassen Münsterland Giro</t>
+  </si>
+  <si>
+    <t>Florian Dauphin</t>
+  </si>
+  <si>
+    <t>Giro dell'Emilia</t>
+  </si>
+  <si>
+    <t>European Continental Championships- Road Race</t>
   </si>
 </sst>
 </file>
@@ -2014,20 +2026,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M189"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M192"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="27" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="13" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2068,7 +2080,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46042</v>
       </c>
@@ -2109,7 +2121,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46043</v>
       </c>
@@ -2150,7 +2162,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46044</v>
       </c>
@@ -2191,7 +2203,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46045</v>
       </c>
@@ -2232,7 +2244,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46046</v>
       </c>
@@ -2273,7 +2285,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46047</v>
       </c>
@@ -2314,7 +2326,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -2355,7 +2367,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46057</v>
       </c>
@@ -2396,7 +2408,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46058</v>
       </c>
@@ -2437,7 +2449,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46059</v>
       </c>
@@ -2478,7 +2490,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46060</v>
       </c>
@@ -2519,7 +2531,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46061</v>
       </c>
@@ -2560,7 +2572,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46069</v>
       </c>
@@ -2601,7 +2613,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46070</v>
       </c>
@@ -2642,7 +2654,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46071</v>
       </c>
@@ -2683,7 +2695,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46071</v>
       </c>
@@ -2724,7 +2736,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46072</v>
       </c>
@@ -2765,7 +2777,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46072</v>
       </c>
@@ -2806,7 +2818,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46073</v>
       </c>
@@ -2847,7 +2859,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46073</v>
       </c>
@@ -2888,7 +2900,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46074</v>
       </c>
@@ -2929,7 +2941,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46074</v>
       </c>
@@ -2970,7 +2982,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46075</v>
       </c>
@@ -3011,7 +3023,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46075</v>
       </c>
@@ -3052,7 +3064,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46081</v>
       </c>
@@ -3093,7 +3105,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46081</v>
       </c>
@@ -3134,7 +3146,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46082</v>
       </c>
@@ -3175,7 +3187,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>46082</v>
       </c>
@@ -3216,7 +3228,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>46088</v>
       </c>
@@ -3257,7 +3269,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>46089</v>
       </c>
@@ -3298,7 +3310,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>46090</v>
       </c>
@@ -3339,7 +3351,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>46091</v>
       </c>
@@ -3380,7 +3392,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>46092</v>
       </c>
@@ -3421,7 +3433,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>46092</v>
       </c>
@@ -3462,7 +3474,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>46093</v>
       </c>
@@ -3503,7 +3515,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>46093</v>
       </c>
@@ -3544,7 +3556,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>46094</v>
       </c>
@@ -3585,7 +3597,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>46094</v>
       </c>
@@ -3626,7 +3638,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>46095</v>
       </c>
@@ -3667,7 +3679,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>46095</v>
       </c>
@@ -3708,7 +3720,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>46096</v>
       </c>
@@ -3749,7 +3761,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>46096</v>
       </c>
@@ -3790,7 +3802,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>46099</v>
       </c>
@@ -3831,7 +3843,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>46099</v>
       </c>
@@ -3872,7 +3884,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>46102</v>
       </c>
@@ -3913,7 +3925,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46104</v>
       </c>
@@ -3954,7 +3966,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46105</v>
       </c>
@@ -3995,7 +4007,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>46106</v>
       </c>
@@ -4036,7 +4048,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>46106</v>
       </c>
@@ -4077,7 +4089,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>46107</v>
       </c>
@@ -4118,7 +4130,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>46108</v>
       </c>
@@ -4159,7 +4171,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>46108</v>
       </c>
@@ -4200,7 +4212,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>46109</v>
       </c>
@@ -4241,7 +4253,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>46110</v>
       </c>
@@ -4282,7 +4294,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>46110</v>
       </c>
@@ -4323,7 +4335,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>46113</v>
       </c>
@@ -4364,7 +4376,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>46116</v>
       </c>
@@ -4405,7 +4417,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>46117</v>
       </c>
@@ -4446,7 +4458,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>46118</v>
       </c>
@@ -4487,7 +4499,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>46119</v>
       </c>
@@ -4528,7 +4540,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>46120</v>
       </c>
@@ -4569,7 +4581,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>46120</v>
       </c>
@@ -4610,7 +4622,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>46121</v>
       </c>
@@ -4651,7 +4663,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>46122</v>
       </c>
@@ -4692,7 +4704,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>46123</v>
       </c>
@@ -4733,7 +4745,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>46124</v>
       </c>
@@ -4774,7 +4786,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>46127</v>
       </c>
@@ -4815,7 +4827,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>46131</v>
       </c>
@@ -4856,7 +4868,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>46132</v>
       </c>
@@ -4897,7 +4909,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>46133</v>
       </c>
@@ -4938,7 +4950,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>46134</v>
       </c>
@@ -4979,7 +4991,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>46134</v>
       </c>
@@ -5020,7 +5032,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>46135</v>
       </c>
@@ -5061,7 +5073,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>46136</v>
       </c>
@@ -5102,7 +5114,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>46138</v>
       </c>
@@ -5143,7 +5155,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>46140</v>
       </c>
@@ -5184,7 +5196,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>46141</v>
       </c>
@@ -5225,7 +5237,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>46142</v>
       </c>
@@ -5266,7 +5278,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>46143</v>
       </c>
@@ -5307,7 +5319,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>46143</v>
       </c>
@@ -5348,7 +5360,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>46144</v>
       </c>
@@ -5389,7 +5401,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>46145</v>
       </c>
@@ -5430,7 +5442,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>46150</v>
       </c>
@@ -5471,7 +5483,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>46151</v>
       </c>
@@ -5512,7 +5524,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>46152</v>
       </c>
@@ -5553,7 +5565,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>46154</v>
       </c>
@@ -5594,7 +5606,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>46155</v>
       </c>
@@ -5635,7 +5647,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>46156</v>
       </c>
@@ -5676,7 +5688,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>46157</v>
       </c>
@@ -5717,7 +5729,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>46158</v>
       </c>
@@ -5758,7 +5770,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>46159</v>
       </c>
@@ -5799,7 +5811,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>46161</v>
       </c>
@@ -5840,7 +5852,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>46162</v>
       </c>
@@ -5881,7 +5893,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>46163</v>
       </c>
@@ -5922,7 +5934,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>46164</v>
       </c>
@@ -5963,7 +5975,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>46165</v>
       </c>
@@ -6004,7 +6016,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>46166</v>
       </c>
@@ -6045,7 +6057,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>46168</v>
       </c>
@@ -6086,7 +6098,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>46169</v>
       </c>
@@ -6127,7 +6139,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>46170</v>
       </c>
@@ -6168,7 +6180,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>46171</v>
       </c>
@@ -6209,7 +6221,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>46172</v>
       </c>
@@ -6250,7 +6262,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>46173</v>
       </c>
@@ -6291,7 +6303,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>46180</v>
       </c>
@@ -6332,7 +6344,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>46180</v>
       </c>
@@ -6373,7 +6385,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>46181</v>
       </c>
@@ -6414,7 +6426,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>46183</v>
       </c>
@@ -6455,7 +6467,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>46184</v>
       </c>
@@ -6496,7 +6508,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>46185</v>
       </c>
@@ -6537,7 +6549,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>46186</v>
       </c>
@@ -6578,7 +6590,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>46187</v>
       </c>
@@ -6619,7 +6631,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>46187</v>
       </c>
@@ -6660,7 +6672,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>46190</v>
       </c>
@@ -6701,7 +6713,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>46191</v>
       </c>
@@ -6742,7 +6754,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>46192</v>
       </c>
@@ -6783,7 +6795,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>46193</v>
       </c>
@@ -6824,7 +6836,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>46194</v>
       </c>
@@ -6865,7 +6877,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>46208</v>
       </c>
@@ -6906,7 +6918,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>46209</v>
       </c>
@@ -6947,7 +6959,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>46210</v>
       </c>
@@ -6988,7 +7000,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>46211</v>
       </c>
@@ -7029,7 +7041,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>46212</v>
       </c>
@@ -7070,7 +7082,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>46213</v>
       </c>
@@ -7111,7 +7123,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>46214</v>
       </c>
@@ -7152,7 +7164,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>46215</v>
       </c>
@@ -7193,7 +7205,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>46217</v>
       </c>
@@ -7234,7 +7246,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>46218</v>
       </c>
@@ -7275,7 +7287,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>46219</v>
       </c>
@@ -7316,7 +7328,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>46220</v>
       </c>
@@ -7357,7 +7369,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>46221</v>
       </c>
@@ -7398,7 +7410,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>46222</v>
       </c>
@@ -7439,7 +7451,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>46224</v>
       </c>
@@ -7480,7 +7492,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>46225</v>
       </c>
@@ -7521,7 +7533,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>46226</v>
       </c>
@@ -7562,7 +7574,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>46227</v>
       </c>
@@ -7603,7 +7615,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>46228</v>
       </c>
@@ -7644,7 +7656,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>46229</v>
       </c>
@@ -7685,7 +7697,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>46235</v>
       </c>
@@ -7726,7 +7738,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>46237</v>
       </c>
@@ -7767,7 +7779,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>46238</v>
       </c>
@@ -7808,7 +7820,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>46239</v>
       </c>
@@ -7849,7 +7861,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>46240</v>
       </c>
@@ -7890,7 +7902,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>46241</v>
       </c>
@@ -7931,7 +7943,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>46242</v>
       </c>
@@ -7972,7 +7984,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>46243</v>
       </c>
@@ -8013,7 +8025,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>46250</v>
       </c>
@@ -8054,7 +8066,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>46253</v>
       </c>
@@ -8095,7 +8107,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>46253</v>
       </c>
@@ -8136,7 +8148,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>46254</v>
       </c>
@@ -8177,7 +8189,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>46254</v>
       </c>
@@ -8218,7 +8230,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>46255</v>
       </c>
@@ -8259,7 +8271,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>46255</v>
       </c>
@@ -8300,7 +8312,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>46256</v>
       </c>
@@ -8341,7 +8353,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>46256</v>
       </c>
@@ -8382,7 +8394,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>46256</v>
       </c>
@@ -8423,7 +8435,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>46257</v>
       </c>
@@ -8464,7 +8476,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>46257</v>
       </c>
@@ -8505,7 +8517,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>46257</v>
       </c>
@@ -8546,7 +8558,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>46259</v>
       </c>
@@ -8587,7 +8599,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>46260</v>
       </c>
@@ -8628,7 +8640,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>46261</v>
       </c>
@@ -8669,7 +8681,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>46262</v>
       </c>
@@ -8710,7 +8722,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>46263</v>
       </c>
@@ -8751,7 +8763,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>46264</v>
       </c>
@@ -8792,7 +8804,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>46264</v>
       </c>
@@ -8833,7 +8845,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>46266</v>
       </c>
@@ -8874,7 +8886,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>46267</v>
       </c>
@@ -8915,7 +8927,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>46267</v>
       </c>
@@ -8956,7 +8968,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>46268</v>
       </c>
@@ -8997,7 +9009,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>46268</v>
       </c>
@@ -9038,7 +9050,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>46269</v>
       </c>
@@ -9079,7 +9091,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>46269</v>
       </c>
@@ -9120,7 +9132,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A174" s="3">
         <v>46270</v>
       </c>
@@ -9161,7 +9173,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A175" s="3">
         <v>46271</v>
       </c>
@@ -9202,7 +9214,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A176" s="3">
         <v>46270</v>
       </c>
@@ -9243,7 +9255,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177" s="3">
         <v>46271</v>
       </c>
@@ -9284,7 +9296,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A178" s="3">
         <v>46273</v>
       </c>
@@ -9325,7 +9337,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A179" s="3">
         <v>46274</v>
       </c>
@@ -9366,7 +9378,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A180" s="3">
         <v>46275</v>
       </c>
@@ -9407,7 +9419,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>46276</v>
       </c>
@@ -9448,7 +9460,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>46276</v>
       </c>
@@ -9489,7 +9501,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>46277</v>
       </c>
@@ -9530,7 +9542,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>46278</v>
       </c>
@@ -9571,7 +9583,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>46278</v>
       </c>
@@ -9612,7 +9624,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>46275</v>
       </c>
@@ -9653,7 +9665,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>46284</v>
       </c>
@@ -9694,7 +9706,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>46285</v>
       </c>
@@ -9735,7 +9747,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>46292</v>
       </c>
@@ -9774,6 +9786,129 @@
       </c>
       <c r="M189" t="s">
         <v>226</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A190" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B190" t="s">
+        <v>531</v>
+      </c>
+      <c r="C190" t="s">
+        <v>60</v>
+      </c>
+      <c r="D190" t="s">
+        <v>446</v>
+      </c>
+      <c r="E190" t="s">
+        <v>122</v>
+      </c>
+      <c r="F190" t="s">
+        <v>409</v>
+      </c>
+      <c r="G190" t="s">
+        <v>175</v>
+      </c>
+      <c r="H190" t="s">
+        <v>161</v>
+      </c>
+      <c r="I190" t="s">
+        <v>532</v>
+      </c>
+      <c r="J190" t="s">
+        <v>209</v>
+      </c>
+      <c r="K190" t="s">
+        <v>124</v>
+      </c>
+      <c r="L190" t="s">
+        <v>287</v>
+      </c>
+      <c r="M190" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A191" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B191" t="s">
+        <v>533</v>
+      </c>
+      <c r="C191" t="s">
+        <v>60</v>
+      </c>
+      <c r="D191" t="s">
+        <v>182</v>
+      </c>
+      <c r="E191" t="s">
+        <v>204</v>
+      </c>
+      <c r="F191" t="s">
+        <v>139</v>
+      </c>
+      <c r="G191" t="s">
+        <v>296</v>
+      </c>
+      <c r="H191" t="s">
+        <v>180</v>
+      </c>
+      <c r="I191" t="s">
+        <v>226</v>
+      </c>
+      <c r="J191" t="s">
+        <v>244</v>
+      </c>
+      <c r="K191" t="s">
+        <v>39</v>
+      </c>
+      <c r="L191" t="s">
+        <v>160</v>
+      </c>
+      <c r="M191" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A192" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B192" t="s">
+        <v>534</v>
+      </c>
+      <c r="C192" t="s">
+        <v>60</v>
+      </c>
+      <c r="D192" t="s">
+        <v>74</v>
+      </c>
+      <c r="E192" t="s">
+        <v>218</v>
+      </c>
+      <c r="F192" t="s">
+        <v>192</v>
+      </c>
+      <c r="G192" t="s">
+        <v>488</v>
+      </c>
+      <c r="H192" t="s">
+        <v>82</v>
+      </c>
+      <c r="I192" t="s">
+        <v>313</v>
+      </c>
+      <c r="J192" t="s">
+        <v>94</v>
+      </c>
+      <c r="K192" t="s">
+        <v>421</v>
+      </c>
+      <c r="L192" t="s">
+        <v>413</v>
+      </c>
+      <c r="M192" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DPshonyak\OneDrive - BluCurrent Credit Union\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9B13DC4-226E-42DF-84DD-1977783972A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{F9B13DC4-226E-42DF-84DD-1977783972A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40279D86-133B-4D84-9040-A23A07AD1747}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2305" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2305" uniqueCount="534">
   <si>
     <t>Date</t>
   </si>
@@ -1610,9 +1610,6 @@
   </si>
   <si>
     <t>Kasper Asgreen</t>
-  </si>
-  <si>
-    <t>Mathieu Van Der Poel</t>
   </si>
   <si>
     <t>World Championships - Road Race</t>
@@ -9752,7 +9749,7 @@
         <v>46292</v>
       </c>
       <c r="B189" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C189" t="s">
         <v>60</v>
@@ -9764,7 +9761,7 @@
         <v>439</v>
       </c>
       <c r="F189" t="s">
-        <v>529</v>
+        <v>171</v>
       </c>
       <c r="G189" t="s">
         <v>289</v>
@@ -9793,7 +9790,7 @@
         <v>46298</v>
       </c>
       <c r="B190" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C190" t="s">
         <v>60</v>
@@ -9814,7 +9811,7 @@
         <v>161</v>
       </c>
       <c r="I190" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="J190" t="s">
         <v>209</v>
@@ -9834,7 +9831,7 @@
         <v>46298</v>
       </c>
       <c r="B191" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C191" t="s">
         <v>60</v>
@@ -9875,7 +9872,7 @@
         <v>46299</v>
       </c>
       <c r="B192" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C192" t="s">
         <v>60</v>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{F9B13DC4-226E-42DF-84DD-1977783972A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40279D86-133B-4D84-9040-A23A07AD1747}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{F9B13DC4-226E-42DF-84DD-1977783972A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EAC2FA4-D90A-42CC-97F5-606B0506677E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2305" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2317" uniqueCount="536">
   <si>
     <t>Date</t>
   </si>
@@ -1625,6 +1625,12 @@
   </si>
   <si>
     <t>European Continental Championships- Road Race</t>
+  </si>
+  <si>
+    <t>Jhonatan Narvaez</t>
+  </si>
+  <si>
+    <t>Tre Valli Varesine</t>
   </si>
 </sst>
 </file>
@@ -2023,20 +2029,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M192"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M193"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="27" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="13" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2077,7 +2083,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46042</v>
       </c>
@@ -2118,7 +2124,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46043</v>
       </c>
@@ -2159,7 +2165,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46044</v>
       </c>
@@ -2200,7 +2206,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46045</v>
       </c>
@@ -2241,7 +2247,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46046</v>
       </c>
@@ -2282,7 +2288,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46047</v>
       </c>
@@ -2323,7 +2329,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -2364,7 +2370,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46057</v>
       </c>
@@ -2405,7 +2411,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46058</v>
       </c>
@@ -2446,7 +2452,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46059</v>
       </c>
@@ -2487,7 +2493,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46060</v>
       </c>
@@ -2528,7 +2534,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46061</v>
       </c>
@@ -2569,7 +2575,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46069</v>
       </c>
@@ -2610,7 +2616,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46070</v>
       </c>
@@ -2651,7 +2657,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46071</v>
       </c>
@@ -2692,7 +2698,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46071</v>
       </c>
@@ -2733,7 +2739,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46072</v>
       </c>
@@ -2774,7 +2780,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46072</v>
       </c>
@@ -2815,7 +2821,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46073</v>
       </c>
@@ -2856,7 +2862,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46073</v>
       </c>
@@ -2897,7 +2903,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46074</v>
       </c>
@@ -2938,7 +2944,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46074</v>
       </c>
@@ -2979,7 +2985,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46075</v>
       </c>
@@ -3020,7 +3026,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46075</v>
       </c>
@@ -3061,7 +3067,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46081</v>
       </c>
@@ -3102,7 +3108,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46081</v>
       </c>
@@ -3143,7 +3149,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46082</v>
       </c>
@@ -3184,7 +3190,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46082</v>
       </c>
@@ -3225,7 +3231,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46088</v>
       </c>
@@ -3266,7 +3272,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46089</v>
       </c>
@@ -3307,7 +3313,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>46090</v>
       </c>
@@ -3348,7 +3354,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>46091</v>
       </c>
@@ -3389,7 +3395,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>46092</v>
       </c>
@@ -3430,7 +3436,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>46092</v>
       </c>
@@ -3471,7 +3477,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>46093</v>
       </c>
@@ -3512,7 +3518,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>46093</v>
       </c>
@@ -3553,7 +3559,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>46094</v>
       </c>
@@ -3594,7 +3600,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>46094</v>
       </c>
@@ -3635,7 +3641,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>46095</v>
       </c>
@@ -3676,7 +3682,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>46095</v>
       </c>
@@ -3717,7 +3723,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>46096</v>
       </c>
@@ -3758,7 +3764,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>46096</v>
       </c>
@@ -3799,7 +3805,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>46099</v>
       </c>
@@ -3840,7 +3846,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>46099</v>
       </c>
@@ -3881,7 +3887,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>46102</v>
       </c>
@@ -3922,7 +3928,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46104</v>
       </c>
@@ -3963,7 +3969,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46105</v>
       </c>
@@ -4004,7 +4010,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>46106</v>
       </c>
@@ -4045,7 +4051,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>46106</v>
       </c>
@@ -4086,7 +4092,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>46107</v>
       </c>
@@ -4127,7 +4133,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>46108</v>
       </c>
@@ -4168,7 +4174,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>46108</v>
       </c>
@@ -4209,7 +4215,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>46109</v>
       </c>
@@ -4250,7 +4256,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>46110</v>
       </c>
@@ -4291,7 +4297,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>46110</v>
       </c>
@@ -4332,7 +4338,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>46113</v>
       </c>
@@ -4373,7 +4379,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>46116</v>
       </c>
@@ -4414,7 +4420,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>46117</v>
       </c>
@@ -4455,7 +4461,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>46118</v>
       </c>
@@ -4496,7 +4502,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>46119</v>
       </c>
@@ -4537,7 +4543,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>46120</v>
       </c>
@@ -4578,7 +4584,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>46120</v>
       </c>
@@ -4619,7 +4625,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>46121</v>
       </c>
@@ -4660,7 +4666,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>46122</v>
       </c>
@@ -4701,7 +4707,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>46123</v>
       </c>
@@ -4742,7 +4748,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>46124</v>
       </c>
@@ -4783,7 +4789,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>46127</v>
       </c>
@@ -4824,7 +4830,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>46131</v>
       </c>
@@ -4865,7 +4871,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>46132</v>
       </c>
@@ -4906,7 +4912,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>46133</v>
       </c>
@@ -4947,7 +4953,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>46134</v>
       </c>
@@ -4988,7 +4994,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>46134</v>
       </c>
@@ -5029,7 +5035,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>46135</v>
       </c>
@@ -5070,7 +5076,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>46136</v>
       </c>
@@ -5111,7 +5117,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>46138</v>
       </c>
@@ -5152,7 +5158,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>46140</v>
       </c>
@@ -5193,7 +5199,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>46141</v>
       </c>
@@ -5234,7 +5240,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>46142</v>
       </c>
@@ -5275,7 +5281,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>46143</v>
       </c>
@@ -5316,7 +5322,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>46143</v>
       </c>
@@ -5357,7 +5363,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>46144</v>
       </c>
@@ -5398,7 +5404,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>46145</v>
       </c>
@@ -5439,7 +5445,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>46150</v>
       </c>
@@ -5480,7 +5486,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>46151</v>
       </c>
@@ -5521,7 +5527,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>46152</v>
       </c>
@@ -5562,7 +5568,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>46154</v>
       </c>
@@ -5603,7 +5609,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>46155</v>
       </c>
@@ -5644,7 +5650,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>46156</v>
       </c>
@@ -5685,7 +5691,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>46157</v>
       </c>
@@ -5726,7 +5732,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>46158</v>
       </c>
@@ -5767,7 +5773,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>46159</v>
       </c>
@@ -5808,7 +5814,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>46161</v>
       </c>
@@ -5849,7 +5855,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>46162</v>
       </c>
@@ -5890,7 +5896,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>46163</v>
       </c>
@@ -5931,7 +5937,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>46164</v>
       </c>
@@ -5972,7 +5978,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>46165</v>
       </c>
@@ -6013,7 +6019,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>46166</v>
       </c>
@@ -6054,7 +6060,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>46168</v>
       </c>
@@ -6095,7 +6101,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>46169</v>
       </c>
@@ -6136,7 +6142,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>46170</v>
       </c>
@@ -6177,7 +6183,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>46171</v>
       </c>
@@ -6218,7 +6224,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>46172</v>
       </c>
@@ -6259,7 +6265,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>46173</v>
       </c>
@@ -6300,7 +6306,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>46180</v>
       </c>
@@ -6341,7 +6347,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>46180</v>
       </c>
@@ -6382,7 +6388,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>46181</v>
       </c>
@@ -6423,7 +6429,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>46183</v>
       </c>
@@ -6464,7 +6470,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>46184</v>
       </c>
@@ -6505,7 +6511,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>46185</v>
       </c>
@@ -6546,7 +6552,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>46186</v>
       </c>
@@ -6587,7 +6593,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>46187</v>
       </c>
@@ -6628,7 +6634,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>46187</v>
       </c>
@@ -6669,7 +6675,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>46190</v>
       </c>
@@ -6710,7 +6716,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>46191</v>
       </c>
@@ -6751,7 +6757,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>46192</v>
       </c>
@@ -6792,7 +6798,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>46193</v>
       </c>
@@ -6833,7 +6839,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>46194</v>
       </c>
@@ -6874,7 +6880,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>46208</v>
       </c>
@@ -6915,7 +6921,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>46209</v>
       </c>
@@ -6956,7 +6962,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>46210</v>
       </c>
@@ -6997,7 +7003,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>46211</v>
       </c>
@@ -7038,7 +7044,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>46212</v>
       </c>
@@ -7079,7 +7085,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>46213</v>
       </c>
@@ -7120,7 +7126,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>46214</v>
       </c>
@@ -7161,7 +7167,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>46215</v>
       </c>
@@ -7202,7 +7208,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>46217</v>
       </c>
@@ -7243,7 +7249,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>46218</v>
       </c>
@@ -7284,7 +7290,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>46219</v>
       </c>
@@ -7325,7 +7331,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>46220</v>
       </c>
@@ -7366,7 +7372,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>46221</v>
       </c>
@@ -7407,7 +7413,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>46222</v>
       </c>
@@ -7448,7 +7454,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>46224</v>
       </c>
@@ -7489,7 +7495,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>46225</v>
       </c>
@@ -7530,7 +7536,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>46226</v>
       </c>
@@ -7571,7 +7577,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>46227</v>
       </c>
@@ -7612,7 +7618,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>46228</v>
       </c>
@@ -7653,7 +7659,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>46229</v>
       </c>
@@ -7694,7 +7700,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>46235</v>
       </c>
@@ -7735,7 +7741,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>46237</v>
       </c>
@@ -7776,7 +7782,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>46238</v>
       </c>
@@ -7817,7 +7823,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>46239</v>
       </c>
@@ -7858,7 +7864,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>46240</v>
       </c>
@@ -7899,7 +7905,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>46241</v>
       </c>
@@ -7940,7 +7946,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>46242</v>
       </c>
@@ -7981,7 +7987,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>46243</v>
       </c>
@@ -8022,7 +8028,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>46250</v>
       </c>
@@ -8063,7 +8069,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>46253</v>
       </c>
@@ -8104,7 +8110,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>46253</v>
       </c>
@@ -8145,7 +8151,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>46254</v>
       </c>
@@ -8186,7 +8192,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>46254</v>
       </c>
@@ -8227,7 +8233,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>46255</v>
       </c>
@@ -8268,7 +8274,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>46255</v>
       </c>
@@ -8309,7 +8315,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>46256</v>
       </c>
@@ -8350,7 +8356,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>46256</v>
       </c>
@@ -8391,7 +8397,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>46256</v>
       </c>
@@ -8432,7 +8438,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>46257</v>
       </c>
@@ -8473,7 +8479,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>46257</v>
       </c>
@@ -8514,7 +8520,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>46257</v>
       </c>
@@ -8555,7 +8561,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>46259</v>
       </c>
@@ -8596,7 +8602,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>46260</v>
       </c>
@@ -8637,7 +8643,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>46261</v>
       </c>
@@ -8678,7 +8684,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>46262</v>
       </c>
@@ -8719,7 +8725,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>46263</v>
       </c>
@@ -8760,7 +8766,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>46264</v>
       </c>
@@ -8801,7 +8807,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>46264</v>
       </c>
@@ -8842,7 +8848,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>46266</v>
       </c>
@@ -8883,7 +8889,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>46267</v>
       </c>
@@ -8924,7 +8930,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>46267</v>
       </c>
@@ -8965,7 +8971,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>46268</v>
       </c>
@@ -9006,7 +9012,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>46268</v>
       </c>
@@ -9047,7 +9053,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>46269</v>
       </c>
@@ -9088,7 +9094,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>46269</v>
       </c>
@@ -9129,7 +9135,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A174" s="3">
         <v>46270</v>
       </c>
@@ -9170,7 +9176,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" s="3">
         <v>46271</v>
       </c>
@@ -9211,7 +9217,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A176" s="3">
         <v>46270</v>
       </c>
@@ -9252,7 +9258,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A177" s="3">
         <v>46271</v>
       </c>
@@ -9293,7 +9299,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A178" s="3">
         <v>46273</v>
       </c>
@@ -9334,7 +9340,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A179" s="3">
         <v>46274</v>
       </c>
@@ -9375,7 +9381,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A180" s="3">
         <v>46275</v>
       </c>
@@ -9416,7 +9422,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>46276</v>
       </c>
@@ -9457,7 +9463,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>46276</v>
       </c>
@@ -9498,7 +9504,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>46277</v>
       </c>
@@ -9539,7 +9545,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>46278</v>
       </c>
@@ -9580,7 +9586,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>46278</v>
       </c>
@@ -9621,7 +9627,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>46275</v>
       </c>
@@ -9662,7 +9668,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>46284</v>
       </c>
@@ -9703,7 +9709,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>46285</v>
       </c>
@@ -9744,7 +9750,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>46292</v>
       </c>
@@ -9785,7 +9791,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>46298</v>
       </c>
@@ -9826,7 +9832,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>46298</v>
       </c>
@@ -9867,7 +9873,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>46299</v>
       </c>
@@ -9906,6 +9912,47 @@
       </c>
       <c r="M192" t="s">
         <v>216</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A193" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B193" t="s">
+        <v>535</v>
+      </c>
+      <c r="C193" t="s">
+        <v>60</v>
+      </c>
+      <c r="D193" t="s">
+        <v>167</v>
+      </c>
+      <c r="E193" t="s">
+        <v>204</v>
+      </c>
+      <c r="F193" t="s">
+        <v>180</v>
+      </c>
+      <c r="G193" t="s">
+        <v>289</v>
+      </c>
+      <c r="H193" t="s">
+        <v>456</v>
+      </c>
+      <c r="I193" t="s">
+        <v>307</v>
+      </c>
+      <c r="J193" t="s">
+        <v>192</v>
+      </c>
+      <c r="K193" t="s">
+        <v>371</v>
+      </c>
+      <c r="L193" t="s">
+        <v>534</v>
+      </c>
+      <c r="M193" t="s">
+        <v>259</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{F9B13DC4-226E-42DF-84DD-1977783972A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EAC2FA4-D90A-42CC-97F5-606B0506677E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CF8E407-D2EA-4B0C-8A1B-9461E93E094F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2317" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2329" uniqueCount="538">
   <si>
     <t>Date</t>
   </si>
@@ -1631,6 +1631,12 @@
   </si>
   <si>
     <t>Tre Valli Varesine</t>
+  </si>
+  <si>
+    <t>Fred Wright</t>
+  </si>
+  <si>
+    <t>Gran Piemonte</t>
   </si>
 </sst>
 </file>
@@ -2029,7 +2035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M193"/>
+  <dimension ref="A1:M194"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -9953,6 +9959,47 @@
       </c>
       <c r="M193" t="s">
         <v>259</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A194" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B194" t="s">
+        <v>537</v>
+      </c>
+      <c r="C194" t="s">
+        <v>60</v>
+      </c>
+      <c r="D194" t="s">
+        <v>191</v>
+      </c>
+      <c r="E194" t="s">
+        <v>50</v>
+      </c>
+      <c r="F194" t="s">
+        <v>388</v>
+      </c>
+      <c r="G194" t="s">
+        <v>194</v>
+      </c>
+      <c r="H194" t="s">
+        <v>189</v>
+      </c>
+      <c r="I194" t="s">
+        <v>536</v>
+      </c>
+      <c r="J194" t="s">
+        <v>281</v>
+      </c>
+      <c r="K194" t="s">
+        <v>439</v>
+      </c>
+      <c r="L194" t="s">
+        <v>35</v>
+      </c>
+      <c r="M194" t="s">
+        <v>521</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -1627,7 +1627,7 @@
     <t>European Continental Championships- Road Race</t>
   </si>
   <si>
-    <t>Jhonatan Narvaez</t>
+    <t>Jhonatan Narváez</t>
   </si>
   <si>
     <t>Tre Valli Varesine</t>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CF8E407-D2EA-4B0C-8A1B-9461E93E094F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{72F01309-B255-448C-A1B3-AC707A4A958A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2329" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2365" uniqueCount="545">
   <si>
     <t>Date</t>
   </si>
@@ -1637,6 +1637,27 @@
   </si>
   <si>
     <t>Gran Piemonte</t>
+  </si>
+  <si>
+    <t>Il Lombardia</t>
+  </si>
+  <si>
+    <t>Paris - Tours Elite</t>
+  </si>
+  <si>
+    <t>Giro del Veneto</t>
+  </si>
+  <si>
+    <t>Matys Grisel</t>
+  </si>
+  <si>
+    <t>Florian Sénéchal</t>
+  </si>
+  <si>
+    <t>Roger Adrià</t>
+  </si>
+  <si>
+    <t>Clément Izquierdo</t>
   </si>
 </sst>
 </file>
@@ -2035,13 +2056,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M194"/>
+  <dimension ref="A1:M197"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="27" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="28.5703125" bestFit="1" customWidth="1"/>
@@ -10000,6 +10021,129 @@
       </c>
       <c r="M194" t="s">
         <v>521</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A195" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B195" t="s">
+        <v>538</v>
+      </c>
+      <c r="C195" t="s">
+        <v>60</v>
+      </c>
+      <c r="D195" t="s">
+        <v>137</v>
+      </c>
+      <c r="E195" t="s">
+        <v>384</v>
+      </c>
+      <c r="F195" t="s">
+        <v>218</v>
+      </c>
+      <c r="G195" t="s">
+        <v>74</v>
+      </c>
+      <c r="H195" t="s">
+        <v>79</v>
+      </c>
+      <c r="I195" t="s">
+        <v>204</v>
+      </c>
+      <c r="J195" t="s">
+        <v>307</v>
+      </c>
+      <c r="K195" t="s">
+        <v>192</v>
+      </c>
+      <c r="L195" t="s">
+        <v>37</v>
+      </c>
+      <c r="M195" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A196" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B196" t="s">
+        <v>539</v>
+      </c>
+      <c r="C196" t="s">
+        <v>60</v>
+      </c>
+      <c r="D196" t="s">
+        <v>277</v>
+      </c>
+      <c r="E196" t="s">
+        <v>235</v>
+      </c>
+      <c r="F196" t="s">
+        <v>173</v>
+      </c>
+      <c r="G196" t="s">
+        <v>541</v>
+      </c>
+      <c r="H196" t="s">
+        <v>279</v>
+      </c>
+      <c r="I196" t="s">
+        <v>190</v>
+      </c>
+      <c r="J196" t="s">
+        <v>526</v>
+      </c>
+      <c r="K196" t="s">
+        <v>232</v>
+      </c>
+      <c r="L196" t="s">
+        <v>542</v>
+      </c>
+      <c r="M196" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A197" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B197" t="s">
+        <v>540</v>
+      </c>
+      <c r="C197" t="s">
+        <v>60</v>
+      </c>
+      <c r="D197" t="s">
+        <v>514</v>
+      </c>
+      <c r="E197" t="s">
+        <v>50</v>
+      </c>
+      <c r="F197" t="s">
+        <v>317</v>
+      </c>
+      <c r="G197" t="s">
+        <v>463</v>
+      </c>
+      <c r="H197" t="s">
+        <v>192</v>
+      </c>
+      <c r="I197" t="s">
+        <v>245</v>
+      </c>
+      <c r="J197" t="s">
+        <v>543</v>
+      </c>
+      <c r="K197" t="s">
+        <v>544</v>
+      </c>
+      <c r="L197" t="s">
+        <v>371</v>
+      </c>
+      <c r="M197" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
